--- a/检查项列表.xlsx
+++ b/检查项列表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\git\autochk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E23A0F-B30E-4D31-820B-08DE6B727F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A42266-97E0-44A7-A5F6-49C6C7AFE9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3CD95B25-7CCF-4613-BB9D-8113267FE491}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="166">
   <si>
     <t>Ana_Osparameter</t>
   </si>
@@ -636,6 +636,10 @@
   <si>
     <t>instshtp.Recovery_usage</t>
   </si>
+  <si>
+    <t>rule.Dbrule.Db_shp_pct.Result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -707,11 +711,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1060,925 +1061,927 @@
   <dimension ref="A2:E97"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="D19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="31" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E35" s="3" t="s">
+      <c r="D35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>64</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
+      <c r="A62" t="s">
         <v>98</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D66" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D67" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D68" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D69" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D70" s="2"/>
+      <c r="D70" s="1"/>
     </row>
     <row r="71" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D71" s="2"/>
+      <c r="D71" s="1"/>
     </row>
     <row r="72" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D72" s="2"/>
+      <c r="C72" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="73" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
     </row>
     <row r="74" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D74" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D77" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D78" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D80" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D81" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="D82" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D83" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A85" s="2" t="s">
+      <c r="A85" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="D85" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D86" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D87" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D88" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="D89" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D90" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D91" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="31.5" x14ac:dyDescent="0.2">
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E92" s="4" t="s">
+      <c r="D92" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="D93" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C97" s="1">
+      <c r="C97">
         <f>1-10/85</f>
         <v>0.88235294117647056</v>
       </c>
